--- a/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What core problem does object-oriented programming solve compared to tracking related data in several parallel lists or dictionaries?</t>
+          <t>A ride-hailing app currently tracks driver names, car numbers, and ratings in three separate parallel lists that all have to stay in sync by index. What core problem does object-oriented programming solve compared to tracking related data in several parallel lists or dictionaries?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -907,7 +907,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A school app originally tracked students using three separate parallel lists for names, roll numbers, and attendance, all synced by matching index positions.
+```python
 names = ["Asha", "Ravi"]
 roll_numbers = [101, 102]
 attendance = {101: 92, 102: 78}
@@ -990,7 +991,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app defines a Student class with a method that checks whether a student's marks meet the passing threshold, then checks one student's result.
+```python
 class Student:
     def has_passed(self):
         return self.marks &gt;= 40
@@ -1076,7 +1078,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app creates a Student object for a newly enrolled student, passing in the name and marks at creation time through the constructor.
+```python
 class Student:
     def __init__(self, name, marks):
         self.name = name
@@ -1162,7 +1165,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app builds a list of Student objects and loops through them to print each student's pass/fail report card.
+```python
 class Student:
     def __init__(self, name, marks):
         self.name = name
@@ -1329,7 +1333,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A banking app currently represents an account as a plain dictionary with a balance key, and a standalone function withdraws money by checking and updating that dictionary directly.
+```python
 account = {"balance": 1000}
 def withdraw(acc, amount):
     if amount &lt;= acc["balance"]:
@@ -1514,7 +1519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>According to the motivation for OOP, what does modeling a 'thing' as a class actually bundle together?</t>
+          <t>A fitness app wants to model each user as a single bundled unit of name, age, and daily step count, rather than tracking behavior and data in unrelated places. According to the motivation for OOP, what does modeling a 'thing' as a class actually bundle together?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1592,7 +1597,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app upgrades from three parallel lists to storing each student's details together in one dictionary, keyed by field name.
+```python
 asha = {"name": "Asha", "roll_number": 101, "attendance": 92}
 ```
 Why is this single dictionary an improvement over three parallel lists, but still not as good as a class?</t>
@@ -1673,7 +1679,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>An online store currently tracks one customer's order using three separate variables for items, prices, and customer name, instead of one bundled structure.
+```python
 order_items = ["Notebook", "Pen Set"]
 order_prices = [120, 80]
 order_customer = "Ravi"
@@ -1756,7 +1763,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why does changing one object's data never affect another object, even when both were built from the identical class?</t>
+          <t>A school's gradebook app creates a fresh Student object for every new admission and updates one student's marks without expecting any other student's record to change. Why does changing one object's data never affect another object, even when both were built from the identical class?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1834,7 +1841,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A program creates fifty Student objects from the same Student class. What is true about these fifty objects?</t>
+          <t>A school enrollment system creates a new Student object for each of its fifty enrolled students at the start of the year, all built from the same Student class. What is true about these fifty objects?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1912,7 +1919,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app defines an empty Student class and then creates two separate student objects, Asha and Ravi, from it.
+```python
 class Student:
     pass
 asha = Student()
@@ -1997,7 +2005,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"A bank account has a balance and an account holder's name." versus "Ravi's savings account, with a balance of 5000." Which is the class description and which is the object?</t>
+          <t>A banking app's documentation describes accounts in general terms, then separately describes one specific customer's actual account. "A bank account has a balance and an account holder's name." versus "Ravi's savings account, with a balance of 5000." Which is the class description and which is the object?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2075,7 +2083,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In the cookie cutter analogy for classes and objects, what does the cookie cutter itself represent?</t>
+          <t>A teacher explaining OOP to new students compares a class to a cookie cutter used to stamp out many cookies. In this cookie cutter analogy for classes and objects, what does the cookie cutter itself represent?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2153,7 +2161,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which code correctly defines an empty Student class?</t>
+          <t>A gradebook app is about to model each enrolled student, so a developer needs to start with a bare-bones Student class before adding any attributes. Which code correctly defines an empty Student class?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2231,7 +2239,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>By Python convention, how should a class name like 'student' typically be written?</t>
+          <t>A gradebook app's developer is naming a new class meant to represent an individual student record and wants to follow standard Python naming conventions. By Python convention, how should a class name like 'student' typically be written?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2410,7 +2418,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A banking app defines an empty BankAccount class and creates an account object, then tries to read a balance attribute that was never set on it.
+```python
 class BankAccount:
     pass
 acc = BankAccount()
@@ -2494,7 +2503,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app creates two separate Student objects and updates one student's marks after a re-evaluation, while checking that the other student's marks stay unaffected.
+```python
 class Student:
     pass
 asha = Student()
@@ -2582,7 +2592,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app creates a bare Student object and then tries to read its name attribute before that attribute has ever been assigned.
+```python
 class Student:
     pass
 meera = Student()
@@ -2666,7 +2677,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What is the single most important idea about where attributes set with `obj.attribute` = value actually live?</t>
+          <t>A gradebook app lets a developer attach a marks attribute to a Student object on the fly using dot notation, without declaring it anywhere inside the class body. What is the single most important idea about where attributes set with `obj.attribute` = value actually live?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2744,7 +2755,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app defines a greet method on the Student class, then creates two separate student objects, each with their own name, and greets both.
+```python
 class Student:
     def greet(self):
         print(f"Hello, I am {self.name}.")
@@ -2833,7 +2845,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app's developer defines a greet method on the Student class but forgets to include the self parameter, then calls it on a student object.
+```python
 class Student:
     def greet():
         print("Hello!")
@@ -2918,7 +2931,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What does the term 'instantiation' refer to in Python's class system?</t>
+          <t>A teacher explaining classes says 'we instantiate a Student' every time a new student record is created in the gradebook app. What does the term 'instantiation' refer to in Python's class system?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2996,7 +3009,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which line correctly attaches a name attribute with the value 'Asha' to an object called asha?</t>
+          <t>A gradebook app needs to attach a name to a freshly created Student object called asha, using dot notation rather than a constructor. Which line correctly attaches a name attribute with the value 'Asha' to an object called asha?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3074,7 +3087,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app's report method needs to reuse the pass/fail check already defined in another method on the same Student object.
+```python
 class Student:
     def has_passed(self):
         return self.marks &gt;= 40
@@ -3163,7 +3177,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app's Student constructor is supposed to take a name, roll number, and marks, but a new admission is registered with the roll number missing.
+```python
 class Student:
     def __init__(self, name, roll_number, marks):
         self.name = name
@@ -3350,7 +3365,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Compared to setting attributes by hand after `Student()` and only discovering a missing one later when some method crashes, what advantage does enforcing required arguments inside `__init__` provide?</t>
+          <t>A gradebook app's Student class requires name and marks to be supplied whenever a new student is created, so a missing value is caught immediately instead of surfacing later. Compared to setting attributes by hand after `Student()` and only discovering a missing one later when some method crashes, what advantage does enforcing required arguments inside `__init__` provide?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3428,7 +3443,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app assigns letter grades to students based on their marks, using a grade method defined on the Student class.
+```python
 class Student:
     def __init__(self, name, marks):
         self.name = name
@@ -3597,7 +3613,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A school admits a new student before any marks have been entered, relying on the Student class's default value for marks.
+```python
 class Student:
     def __init__(self, name, roll_number, marks=0):
         self.name = name
@@ -3684,7 +3701,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A banking app's BankAccount class blocks a withdrawal that would overdraw the account, and a customer tries to withdraw more than their current balance.
+```python
 class BankAccount:
     def __init__(self, holder, balance=0):
         self.holder = holder
@@ -3776,7 +3794,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How do the Student and BankAccount classes from the walkthrough differ in the kind of real-world thing they model?</t>
+          <t>A school's curriculum team is comparing two of the classes used throughout their app's walkthrough: one for enrolled students and one for bank accounts. How do the Student and BankAccount classes from the walkthrough differ in the kind of real-world thing they model?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3854,7 +3872,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A tourism app's homepage just needs to show today's visitor count and one fixed resort location, two simple standalone values.
+```python
 visitor_count = 47
 trip_stop = ("Resort", 15.2993, 74.1240)
 ```
@@ -3936,7 +3955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the key signal that a real-world thing has outgrown a plain dictionary or tuple and deserves a class instead?</t>
+          <t>A logistics dashboard just needs to display today's total shipments and one fixed warehouse coordinate on screen.
+```python
+visitor_count = 47
+trip_stop = ("Resort", 15.2993, 74.1240)
+```
+Why do neither of these need a class?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4014,7 +4038,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A developer writes a full class with `__init__` and methods just to store a single one-off number, today's visitor count of 47. What is the issue with this design choice?</t>
+          <t>A ticketing app is deciding which pieces of data deserve a full class versus a simple built-in type as the app grows in complexity. What is the key signal that a real-world thing has outgrown a plain dictionary or tuple and deserves a class instead?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4092,21 +4116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
-launch_date = ("2026-06-29",)
-class Event:
-    def __init__(self, name, date, capacity):
-        self.name = name
-        self.date = date
-        self.capacity = capacity
-        self.registered = 0
-    def register(self, count):
-        if self.registered + count &gt; self.capacity:
-            print("Not enough capacity.")
-        else:
-            self.registered += count
-```
-Why does launch_date stay a tuple while Event becomes a class?</t>
+          <t>A tourism app's homepage shows today's visitor count as a single number, but a developer insists on building a whole class with `__init__` and methods just for that one value. What is the issue with this design choice?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 9.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 9.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 9.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 9.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>It technically makes programs run measurably and noticeably faster on every single machine</t>
+          <t>It technically forces all code in the program to be written using loops only</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>It technically forces all code in the program to be written using loops only</t>
+          <t>It technically makes programs run measurably and noticeably faster on every single machine every time</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -721,26 +721,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>A class is a blueprint describing a kind of thing; an object is one specific instance built from it</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>They are simply two completely different words for exactly the same identical concept</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>An object is always created well before its class is even defined</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>A class is a blueprint describing a kind of thing; an object is one specific instance built from it</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>A class holds real, actual values; an object is just a plain name</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>They are simply two different words for exactly the same identical concept</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -809,16 +809,16 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>method `greet(self)`: `print("Hello")`</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>def `greet(self)`: `print("Hello")`</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>method `greet(self)`: `print("Hello")`</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -877,26 +877,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>It technically prevents the class from ever being instantiated more than once at all</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>It technically makes the class run measurably faster overall</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>It guarantees every object starts complete by setting attributes automatically at creation time</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>It technically removes the entire need for the self parameter</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>It technically makes the class run measurably faster overall</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>It technically prevents the class from ever being instantiated more than once</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>It guarantees every object starts complete by setting attributes automatically at creation time</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -961,26 +961,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>The name could silently become associated with the wrong roll number and attendance</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Python would technically raise an error automatically in this situation</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Lists technically cannot hold student names as values at all</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>The name could silently become associated with the wrong roll number and attendance</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>The program would crash immediately on the next print</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1048,26 +1048,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>An `AttributeError`</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1135,26 +1135,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>`None` `None`</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Asha 72</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>An error, since `__init__` cannot take extra parameters</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>name marks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>`None` `None`</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Asha 72</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>An error, since `__init__` cannot take extra parameters</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1225,26 +1225,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Asha Pass then Ravi Fail</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Only Ravi Fail is printed</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>An error, since for loops cannot iterate over objects</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Asha Fail then Ravi Pass</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Asha Pass then Ravi Fail</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Only Ravi Fail is printed</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>An error, since for loops cannot iterate over objects</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Attributes set this way can technically never be changed again afterward</t>
+          <t>This approach makes all ten objects share the same attribute values</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>This approach makes all ten objects share the same attribute values</t>
+          <t>It is easy to forget to set an attribute on some object, leaving it incomplete until it later crashes</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>It is easy to forget to set an attribute on some object, leaving it incomplete until it later crashes</t>
+          <t>Attributes set this way can technically never be changed again afterward, ever, under any condition</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1393,21 +1393,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>The withdraw function would technically raise a syntax error immediately</t>
+          <t>The withdraw function would technically raise a syntax error immediately every time</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>Dictionaries technically cannot store any numeric balances at all here</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Other code can directly edit `account["balance"]`, bypassing the withdraw check entirely</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Dictionaries technically cannot store any numeric balances at all here</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1572,21 +1572,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Only the function definitions themselves, never any data</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Both the data and the behaviour that belongs to that data, as one unit</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Only the plain variable names used throughout a program</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Only the function definitions themselves, never any data</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1649,26 +1649,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>It keeps related data together but still cannot attach behaviour directly to the student</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>It is strictly worse than parallel lists in absolutely every conceivable way</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>It technically cannot store more than a single value at once</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>It keeps related data together but still cannot attach behaviour directly to the student</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Dictionaries technically cannot hold student names at all here</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>It is strictly worse than parallel lists in absolutely every way</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1733,26 +1733,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>A function that simply has not yet been written at all</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A single, standalone list containing only customer names</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>A single order, with its items, prices, and customer scattered across variables</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Three completely unrelated values with absolutely nothing in common at all</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>A single order, with its items, prices, and customer scattered across variables</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>A function that simply has not yet been written at all</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>A single, standalone list containing only customer names</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Because technically only one single object can ever exist per class at a time</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Because objects technically become read-only the moment they are created</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Because Python secretly copies the entire class definition for every single change</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Because technically only one single object can ever exist per class at a time</t>
+          <t>Because Python secretly copies the entire class definition for every single change made anywhere</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1889,26 +1889,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>They are all secretly and silently the same identical object underneath</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Only one of them is technically allowed to hold real data at a time</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Creating fifty objects technically requires fifty separate class definitions</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>They share the same blueprint but remain separate, independent objects with their own data</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>They are all secretly and silently the same identical object underneath</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Creating fifty objects technically requires fifty separate class definitions</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Only one of them is technically allowed to hold real data at a time</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1975,26 +1975,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>`True`, but only if both objects happen to be completely empty</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>`False`, because each call to `Student()` produces a separate object</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>An error occurs, since is cannot be used to compare objects</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>`True`, because they both came from the exact same class</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>`True`, but only if both objects happen to be completely empty</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>An error occurs, since is cannot be used to compare objects</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2053,26 +2053,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>The first is the object; the second is the class</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>The first is the class; the second is the object</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Both describe the same object</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Neither describes a class or an object</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Both describe the same object</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>The first is the object; the second is the class</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2131,26 +2131,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>The cookie cutter itself represents an individual object</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>The cookie cutter itself represents a single attribute</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>The cookie cutter itself represents an individual object</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>The cookie cutter represents the self parameter</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>The cookie cutter represents the class, defining the shared shape</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>The cookie cutter represents the self parameter</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2209,26 +2209,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>class Student: pass</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>class Student: end</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>class `Student()`: {}</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>class Student: end</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>define Student: pass</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>class Student: pass</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2287,26 +2287,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>all lowercase, exactly like a variable</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CapitalisedWords (PascalCase), such as Student</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ALL_CAPS, exactly like a constant</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>with a leading underscore, such as _Student</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>all lowercase, exactly like a variable</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>CapitalisedWords (PascalCase), such as Student</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ALL_CAPS, exactly like a constant</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2562,26 +2562,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>95 65</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>95 60</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>100 60</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>95 65</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>95 60</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>90 60</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2647,22 +2647,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It creates name with a default value of 'Unknown'</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>It simply prints an entirely empty string back</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>It raises an `AttributeError`, because name was never set on meera</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>It simply prints the value `None` automatically instead</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It raises an `AttributeError`, because name was never set on meera</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It creates name with a default value of 'Unknown'</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2725,26 +2725,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Attributes are shared across every object of the class automatically</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Attributes belong to the class and cannot vary per object</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Setting an attribute on one object also sets it on all future objects</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Attributes are shared across every object of the class automatically</t>
+          <t>Attributes belong to the individual object, so each object keeps its own independent values</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Attributes belong to the individual object, so each object keeps its own independent values</t>
+          <t>Setting an attribute on one object also silently sets it on all future objects too</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2815,26 +2815,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Hello, I am Asha. then Hello, I am Ravi.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>An error, since self cannot change between calls</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Hello, I am Asha. printed twice</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>An error, since self cannot change between calls</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Hello, I am Ravi. then Hello, I am Ravi.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Hello, I am Asha. then Hello, I am Ravi.</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>It prints 'Hello!' completely normally, since self is entirely optional</t>
+          <t>It prints 'Hello!' followed directly by the object's memory address</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>It prints 'Hello!' followed directly by the object's memory address</t>
+          <t>It raises a `TypeError`, because Python passes asha as an argument greet has no parameter for</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>It raises a `TypeError`, because Python passes asha as an argument greet has no parameter for</t>
+          <t>It prints 'Hello!' completely normally, since self is entirely optional here in Python</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2979,26 +2979,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Renaming an already existing class sometime after it is first defined</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Deleting an object entirely and permanently from computer memory</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>Writing the pass keyword by itself inside an empty class body</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Renaming an already existing class sometime after it is first defined</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>The process of creating an actual object from a class by calling it like a function</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Deleting an object entirely and permanently from computer memory</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3062,17 +3062,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>`asha["name"]` = "Asha"</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>asha::`name = "Asha"`</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>set `asha.name("Asha")`</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>asha::`name = "Asha"`</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>`asha["name"]` = "Asha"</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>It technically cannot reach has_passed without explicitly passing asha as well</t>
+          <t>It manually copies the entire code from has_passed directly into report</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>It manually copies the entire code from has_passed directly into report</t>
+          <t>It technically cannot reach has_passed without also explicitly passing asha as well</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -3234,26 +3234,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>It creates ravi with marks set to 0 automatically</t>
+          <t>It creates ravi with marks set to 0 automatically by default</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>It silently skips setting marks and continues</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>It creates ravi with marks set to `None`</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>It raises a `TypeError` immediately, since marks was not supplied</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It silently skips setting marks and continues</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It creates ravi with marks set to `None`</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3413,26 +3413,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It catches the missing data immediately at creation, instead of producing a broken object that fails later, elsewhere</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>It technically prevents the program from ever raising a `TypeError` of any kind at all</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>There is genuinely no real advantage at all, both approaches fail at the exact same moment</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>There is genuinely no real advantage at all here, both approaches fail at the exact same moment regardless</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>It technically makes the entire class completely impossible to ever subclass later</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It catches the missing data immediately at creation, instead of producing a broken object that fails later, elsewhere</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3505,26 +3505,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>An error, since 30 is too low for any grade</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3583,26 +3583,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>The account balance can go negative, since nothing stops a withdrawal larger than the balance</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The method would technically raise a `TypeError` on absolutely every call</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>deposit would technically stop working correctly as an unintended side effect</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>The account balance can go negative, since nothing stops a withdrawal larger than the balance</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Nothing changes at all, Python automatically prevents negative balances on its own</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>The method would technically raise a `TypeError` on absolutely every call</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3764,26 +3764,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>An error is raised, since balance cannot go below 0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Insufficient balance. then -1000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Withdrew 2000. then -1000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Insufficient balance. then 1000</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Insufficient balance. then -1000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Withdrew 2000. then -1000</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>An error is raised, since balance cannot go below 0</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3842,26 +3842,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Student technically requires far more attributes than BankAccount is ever genuinely able to hold at all</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Student models something mostly static; BankAccount models something that changes constantly and needs protection</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>They are technically identical in absolutely every single conceivable respect</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>BankAccount technically never makes any use of `__init__` at all, only Student does</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Student technically requires far more attributes than BankAccount is ever able to have</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Student models something mostly static; BankAccount models something that changes constantly and needs protection</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3925,26 +3925,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Because Python technically forbids classes with fewer than three total attributes</t>
+          <t>Because classes technically cannot ever hold numbers or tuples as data</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Because classes technically cannot ever hold numbers or tuples as data</t>
+          <t>Because Python technically forbids classes with fewer than three total attributes defined anywhere</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Because neither has behaviour or rules to enforce; they are just standalone values or a fixed group of facts</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Because tuples and classes are technically exactly the same underlying thing</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Because neither has behaviour or rules to enforce; they are just standalone values or a fixed group of facts</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>The thing will technically only ever be created once in the whole entire running program, ever, period</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>The data itself simply needs to be printed out more than one single time</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>The thing will technically only ever be created once in the whole entire running program</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -4086,26 +4086,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>It is needless ceremony, since a single value with no behaviour needs nothing more than a variable</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>There is genuinely no issue at all here, every value should always be wrapped in a class</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>`__init__` would technically refuse to ever run for a single number</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Classes technically cannot ever store simple integer values like 47</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>`__init__` would technically refuse to ever run for a single number</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>There is genuinely no issue at all, every value should always be wrapped in a class</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It is needless ceremony, since a single value with no behaviour needs nothing more than a variable</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4164,26 +4164,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Classes are always faster than tuples for storing dates</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>launch_date has no behaviour to protect, while Event must enforce a capacity rule on every registration</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Tuples cannot hold strings, so a class was required for the date</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>There is no real difference; either could have been written the other way with identical behaviour</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Classes are always faster than tuples for storing dates</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tuples cannot hold strings, so a class was required for the date</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>`self.marks` reaches ravi's own marks attribute, which is 30; since 30 is not greater than or equal to 40, has_passed returns `False`, which is what gets printed.</t>
+          <t>`self.marks` reaches ravi's own marks attribute, which is 30; since 30 is not greater than or equal to 40, `has_passed` returns `False`, which is what gets printed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A developer creates ten Student objects and manually sets .name and .roll_number on each one outside the class. What is the main risk of this approach?</t>
+          <t>A developer creates ten Student objects and manually sets .name and .`roll_number` on each one outside the class. What is the main risk of this approach?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Class names follow CapitalisedWords, sometimes called PascalCase, so 'Student' rather than 'student'; this capital letter is a visual signal to readers that the name refers to a class, the opposite convention from snake_case variables.</t>
+          <t>Class names follow CapitalisedWords, sometimes called PascalCase, so 'Student' rather than 'student'; this capital letter is a visual signal to readers that the name refers to a class, the opposite convention from `snake_case` variables.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3099,7 +3099,7 @@
 asha.marks = 72
 asha.report()
 ```
-How does report reach the logic inside has_passed?</t>
+How does report reach the logic inside `has_passed`?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>It manually copies the entire code from has_passed directly into report</t>
+          <t>It manually copies the entire code from `has_passed` directly into report</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>It technically cannot reach has_passed without also explicitly passing asha as well</t>
+          <t>It technically cannot reach `has_passed` without also explicitly passing asha as well</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marks has a default value of 0 in `__init__`, and since no third argument was supplied when creating new_admission, Python uses that default, so 0 is printed.</t>
+          <t>marks has a default value of 0 in `__init__`, and since no third argument was supplied when creating `new_admission`, Python uses that default, so 0 is printed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>launch_date is a single fixed fact with no behaviour, so a tuple is enough, while an Event has a capacity that must never be exceeded by registrations, a rule that needs to be enforced every time register is called, which is exactly the behaviour-protecting role a class plays.</t>
+          <t>`launch_date` is a single fixed fact with no behaviour, so a tuple is enough, while an Event has a capacity that must never be exceeded by registrations, a rule that needs to be enforced every time register is called, which is exactly the behaviour-protecting role a class plays.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>launch_date has no behaviour to protect, while Event must enforce a capacity rule on every registration</t>
+          <t>`launch_date` has no behaviour to protect, while Event must enforce a capacity rule on every registration</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A developer creates ten Student objects and manually sets .name and .`roll_number` on each one outside the class. What is the main risk of this approach?</t>
+          <t>A developer creates ten Student objects and manually sets `.name` and `.roll_number` on each one outside the class. What is the main risk of this approach?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3957,8 +3957,8 @@
         <is>
           <t>A logistics dashboard just needs to display today's total shipments and one fixed warehouse coordinate on screen.
 ```python
-visitor_count = 47
-trip_stop = ("Resort", 15.2993, 74.1240)
+shipment_count = 47
+warehouse_location = ("Main Depot", 15.2993, 74.1240)
 ```
 Why do neither of these need a class?</t>
         </is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A ticketing app is deciding which pieces of data deserve a full class versus a simple built-in type as the app grows in complexity. What is the key signal that a real-world thing has outgrown a plain dictionary or tuple and deserves a class instead?</t>
+          <t>A ticketing app is deciding which pieces of data deserve a full class versus a simple built-in type as the app grows in complexity. What is the key signal that a real-world thing does NOT need a class, and a plain variable is enough instead?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A tourism app's homepage shows today's visitor count as a single number, but a developer insists on building a whole class with `__init__` and methods just for that one value. What is the issue with this design choice?</t>
+          <t>An event-booking app stores a workshop's fixed launch date as a simple tuple, but models the workshop itself as an Event class with `__init__` and a `register` method. How do `launch_date` and Event differ in whether they need a class?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
